--- a/artfynd/A 17601-2026 artfynd.xlsx
+++ b/artfynd/A 17601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91953586</v>
+        <v>94492300</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Krokom, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462773.0096326948</v>
+        <v>462566</v>
       </c>
       <c r="R2" t="n">
-        <v>7104053.971643656</v>
+        <v>7104084</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,64 +766,55 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94523115</v>
+        <v>91953586</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torshöjden - Sörrun, Jmt</t>
+          <t>Jämtlands län, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462800.7267972961</v>
+        <v>462773</v>
       </c>
       <c r="R3" t="n">
-        <v>7104025.176370968</v>
+        <v>7104054</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +838,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,15 +863,226 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>94492384</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Krokom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>462547</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7104071</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94523115</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Torshöjden - Sörrun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>462801</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7104025</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17601-2026 artfynd.xlsx
+++ b/artfynd/A 17601-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94492300</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94492384</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,8 +1103,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523115</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>